--- a/results/section_2_2_table_2025.xlsx
+++ b/results/section_2_2_table_2025.xlsx
@@ -32,37 +32,37 @@
     <t xml:space="preserve">2010-2019</t>
   </si>
   <si>
-    <t xml:space="preserve">2013-2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023 (projection)</t>
+    <t xml:space="preserve">2014-2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024 (projection)</t>
   </si>
   <si>
     <t xml:space="preserve">GHG</t>
   </si>
   <si>
-    <t xml:space="preserve">31±4.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35±4.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39±5.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45±5.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53±5.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53±5.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55±5.1</t>
+    <t xml:space="preserve">30.9±4.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7±4.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3±5.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1±5.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9±5.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7±5.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3±5.1</t>
   </si>
   <si>
     <t xml:space="preserve">CO2-FFI</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">35.5±2.8</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1±2.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3±3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37±2.9</t>
+    <t xml:space="preserve">36.4±2.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8±3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1±3</t>
   </si>
   <si>
     <t xml:space="preserve">CO2-LULUCF</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">4.9±3.4</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3±3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5±2.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4±2.8</t>
+    <t xml:space="preserve">4.1±2.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6±2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4±3.1</t>
   </si>
   <si>
     <t xml:space="preserve">CH4</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">8.4±2.5</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6±2.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9±2.7</t>
+    <t xml:space="preserve">8.7±2.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2±2.7</t>
   </si>
   <si>
     <t xml:space="preserve">N2O</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">1.4±0.42</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6±0.48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8±0.54</t>
+    <t xml:space="preserve">1.6±0.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8±0.55</t>
   </si>
 </sst>
 </file>

--- a/results/section_2_2_table_2025.xlsx
+++ b/results/section_2_2_table_2025.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t xml:space="preserve">label</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">30.9±4.5</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7±4.6</t>
+    <t xml:space="preserve">34.6±4.6</t>
   </si>
   <si>
     <t xml:space="preserve">39.3±5.1</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">52.9±5.4</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7±5.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3±5.1</t>
+    <t xml:space="preserve">53.6±5.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1±5.1</t>
   </si>
   <si>
     <t xml:space="preserve">CO2-FFI</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">28.9±2.3</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5±2.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4±2.9</t>
+    <t xml:space="preserve">35.4±2.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3±2.9</t>
   </si>
   <si>
     <t xml:space="preserve">37.8±3</t>
@@ -170,25 +170,22 @@
     <t xml:space="preserve">F-gases</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21±0.064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37±0.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52±0.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.84±0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4±0.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6±0.49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8±0.55</t>
+    <t xml:space="preserve">0.2±0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4±0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5±0.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8±0.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4±0.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6±0.5</t>
   </si>
 </sst>
 </file>
@@ -708,7 +705,7 @@
         <v>57</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I7"/>
     </row>

--- a/results/section_2_2_table_2025.xlsx
+++ b/results/section_2_2_table_2025.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t xml:space="preserve">label</t>
   </si>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">53.6±5.2</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1±5.1</t>
+    <t xml:space="preserve">55.4±5.1</t>
   </si>
   <si>
     <t xml:space="preserve">CO2-FFI</t>
@@ -185,7 +185,10 @@
     <t xml:space="preserve">1.4±0.4</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6±0.5</t>
+    <t xml:space="preserve">1.7±0.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9±0.6</t>
   </si>
 </sst>
 </file>
@@ -705,7 +708,7 @@
         <v>57</v>
       </c>
       <c r="H7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I7"/>
     </row>
